--- a/results/final_N33_v5/Trend_Method_Comparison/Excel/Master/Reviewer_Summary.xlsx
+++ b/results/final_N33_v5/Trend_Method_Comparison/Excel/Master/Reviewer_Summary.xlsx
@@ -1314,7 +1314,7 @@
       </c>
       <c r="B2" s="12" t="inlineStr">
         <is>
-          <t>Significant lag-1 autocorrelation (α=0.05) detected at 10/12 stations. rho_1 ranges up to 0.5827. MMK correction factor ranges 1.000–1.0984.</t>
+          <t>Significant lag-1 autocorrelation (α=0.05) detected at 10/12 stations. rho_1 ranges up to 0.5827. MMK correction factor ranges 1.000–2.7251.</t>
         </is>
       </c>
       <c r="C2" s="12" t="inlineStr">
